--- a/sequences/fastseq_conditions_10.xlsx
+++ b/sequences/fastseq_conditions_10.xlsx
@@ -544,77 +544,77 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_35.jpg</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_10.jpg</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_21.jpg</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="I2" t="n">
         <v>5</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="K2" t="n">
         <v>4</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>stimuli/jacket/jacket_01.jpg</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>10</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>stimuli/house/house_10.jpg</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
     </row>
@@ -632,27 +632,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/dog/dog_28.jpg</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_10.jpg</t>
+          <t>stimuli/hand/hand_12.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -664,11 +664,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_01.jpg</t>
+          <t>stimuli/flower/flower_10.jpg</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -720,44 +720,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_16.jpg</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_29.jpg</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_08.jpg</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_01.jpg</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_14.jpg</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="M4" t="n">
         <v>6</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_16.jpg</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_10.jpg</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_29.jpg</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_00.png</t>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
     </row>
@@ -808,44 +808,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>stimuli/house/house_31.jpg</t>
+          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/dog/dog_28.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_01.jpg</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>3</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_12.jpg</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>8</v>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_01.png</t>
@@ -878,7 +878,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_12.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
     </row>
@@ -896,11 +896,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -912,27 +912,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_16.jpg</t>
+          <t>stimuli/bread/bread_29.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/dog/dog_21.jpg</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_29.jpg</t>
+          <t>stimuli/flower/flower_14.jpg</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/dog/dog_21.jpg</t>
         </is>
       </c>
     </row>
@@ -984,43 +984,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_11.jpg</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_10.jpg</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>stimuli/house/house_31.jpg</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="I7" t="n">
         <v>9</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>stimuli/bicycle/bicycle_01.jpg</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_14.jpg</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_04.jpg</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_28.jpg</t>
+          <t>stimuli/hammer/hammer_22.jpg</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/house/house_31.jpg</t>
         </is>
       </c>
     </row>
@@ -1072,43 +1072,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_14.jpg</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_29.jpg</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>stimuli/bread/bread_29.jpg</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>3</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_16.jpg</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>8</v>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
     </row>
@@ -1160,77 +1160,77 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_12.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_10.jpg</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_31.jpg</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>9</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_01.jpg</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="M9" t="n">
         <v>2</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_14.jpg</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>stimuli/bread/bread_04.jpg</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_12.jpg</t>
         </is>
       </c>
     </row>
@@ -1248,77 +1248,77 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_16.jpg</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_29.jpg</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_01.jpg</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_14.jpg</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="K10" t="n">
         <v>6</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_10.jpg</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_16.jpg</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>8</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_10.jpg</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>9</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_29.jpg</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_08.jpg</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>4</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_14.jpg</t>
         </is>
       </c>
     </row>
@@ -1336,43 +1336,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>stimuli/house/house_31.jpg</t>
+          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_28.jpg</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_22.jpg</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>7</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_28.jpg</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>5</v>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_12.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
     </row>
@@ -1424,44 +1424,44 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>stimuli/house/house_10.jpg</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_16.jpg</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="K12" t="n">
         <v>4</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>stimuli/flower/flower_14.jpg</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="M12" t="n">
         <v>6</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>10</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_29.jpg</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>2</v>
-      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_05.png</t>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_14.jpg</t>
+          <t>stimuli/hand/hand_16.jpg</t>
         </is>
       </c>
     </row>
@@ -1512,44 +1512,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_11.jpg</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_14.jpg</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_12.jpg</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_04.jpg</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>stimuli/house/house_31.jpg</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="M13" t="n">
         <v>9</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>10</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_10.jpg</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_12.jpg</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_14.jpg</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>4</v>
-      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_04.png</t>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/house/house_31.jpg</t>
         </is>
       </c>
     </row>
@@ -1600,77 +1600,77 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>stimuli/house/house_10.jpg</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>9</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_21.jpg</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="K14" t="n">
         <v>4</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>10</v>
-      </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_14.jpg</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>6</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_29.jpg</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>2</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_29.jpg</t>
         </is>
       </c>
     </row>
@@ -1688,77 +1688,77 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_11.jpg</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_14.jpg</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_12.jpg</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_10.jpg</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>stimuli/house/house_31.jpg</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="M15" t="n">
         <v>9</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>10</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_10.jpg</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_01.jpg</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
         <is>
           <t>stimuli/chair/chair_14.jpg</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
-        <v>4</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
     </row>
@@ -1776,11 +1776,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1792,61 +1792,61 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_16.jpg</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_01.jpg</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>10</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_14.jpg</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="M16" t="n">
         <v>6</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_10.jpg</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>9</v>
-      </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>stimuli/bicycle/bicycle_29.jpg</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
-        <v>2</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_29.jpg</t>
         </is>
       </c>
     </row>
@@ -1864,43 +1864,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>stimuli/house/house_31.jpg</t>
+          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_10.jpg</t>
+          <t>stimuli/hand/hand_12.jpg</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_12.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_28.jpg</t>
+          <t>stimuli/hammer/hammer_22.jpg</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_01.jpg</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>stimuli/house/house_31.jpg</t>
+          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
     </row>
@@ -1952,11 +1952,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1968,27 +1968,27 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_16.jpg</t>
+          <t>stimuli/bread/bread_29.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_29.jpg</t>
+          <t>stimuli/flower/flower_14.jpg</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -2040,44 +2040,44 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_11.jpg</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_10.jpg</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_04.jpg</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>stimuli/house/house_31.jpg</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="K19" t="n">
         <v>9</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>stimuli/bicycle/bicycle_01.jpg</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="M19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_12.jpg</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_14.jpg</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_04.jpg</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>3</v>
-      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_02.png</t>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_01.jpg</t>
+          <t>stimuli/flower/flower_10.jpg</t>
         </is>
       </c>
     </row>
@@ -2128,11 +2128,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2144,27 +2144,27 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_29.jpg</t>
+          <t>stimuli/flower/flower_14.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_14.jpg</t>
+          <t>stimuli/hand/hand_16.jpg</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2216,44 +2216,44 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_11.jpg</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_12.jpg</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_04.jpg</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_22.jpg</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>stimuli/house/house_31.jpg</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="M21" t="n">
         <v>9</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_10.jpg</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>6</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_12.jpg</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>8</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_28.jpg</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_14.jpg</t>
-        </is>
-      </c>
-      <c r="M21" t="n">
-        <v>4</v>
-      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_01.png</t>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_12.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
     </row>
@@ -2304,11 +2304,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2320,27 +2320,27 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_14.jpg</t>
+          <t>stimuli/hand/hand_16.jpg</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/dog/dog_21.jpg</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/dog/dog_21.jpg</t>
         </is>
       </c>
     </row>
@@ -2392,35 +2392,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_01.jpg</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_10.jpg</t>
+          <t>stimuli/hand/hand_12.jpg</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_28.jpg</t>
+          <t>stimuli/hammer/hammer_22.jpg</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/house/house_31.jpg</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/house/house_31.jpg</t>
         </is>
       </c>
     </row>
@@ -2480,11 +2480,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/dog/dog_21.jpg</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2496,27 +2496,27 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>stimuli/house/house_10.jpg</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>9</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>4</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>10</v>
-      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_29.jpg</t>
+          <t>stimuli/flower/flower_14.jpg</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
     </row>
@@ -2568,44 +2568,44 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_11.jpg</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_10.jpg</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>6</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_28.jpg</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_12.jpg</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>8</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>stimuli/house/house_31.jpg</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="M25" t="n">
         <v>9</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_01.jpg</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>7</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_10.jpg</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>6</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_14.jpg</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
-        <v>4</v>
-      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_04.png</t>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/dog/dog_28.jpg</t>
         </is>
       </c>
     </row>
@@ -2656,43 +2656,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_16.jpg</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_14.jpg</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="K26" t="n">
         <v>6</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_29.jpg</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>3</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_29.jpg</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>2</v>
-      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
     </row>
@@ -2744,77 +2744,77 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_04.jpg</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_14.jpg</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_12.jpg</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="I27" t="n">
         <v>8</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>10</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_10.jpg</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>6</v>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_28.jpg</t>
+          <t>stimuli/hammer/hammer_22.jpg</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
+          <t>stimuli/house/house_31.jpg</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>9</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_14.jpg</t>
-        </is>
-      </c>
-      <c r="M27" t="n">
-        <v>4</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
     </row>
@@ -2832,11 +2832,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2848,27 +2848,27 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/jacket/jacket_01.jpg</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/dog/dog_21.jpg</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/jacket/jacket_01.jpg</t>
         </is>
       </c>
     </row>
@@ -2920,35 +2920,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_10.jpg</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_12.jpg</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_01.jpg</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="I29" t="n">
         <v>2</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_10.jpg</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>6</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_04.jpg</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>3</v>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_28.jpg</t>
+          <t>stimuli/hammer/hammer_22.jpg</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_28.jpg</t>
+          <t>stimuli/hammer/hammer_22.jpg</t>
         </is>
       </c>
     </row>
@@ -3008,77 +3008,77 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_35.jpg</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_10.jpg</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>9</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_29.jpg</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_21.jpg</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="M30" t="n">
         <v>5</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_08.jpg</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>4</v>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
         <is>
           <t>stimuli/bread/bread_29.jpg</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_16.jpg</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>8</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
-        </is>
-      </c>
-      <c r="M30" t="n">
-        <v>7</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_16.jpg</t>
         </is>
       </c>
     </row>
@@ -3096,35 +3096,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_01.jpg</t>
+          <t>stimuli/flower/flower_10.jpg</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_28.jpg</t>
+          <t>stimuli/hammer/hammer_22.jpg</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/house/house_31.jpg</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -3184,11 +3184,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3200,27 +3200,27 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_29.jpg</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_16.jpg</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>8</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_14.jpg</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>6</v>
-      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/jacket/jacket_01.jpg</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_16.jpg</t>
+          <t>stimuli/bread/bread_29.jpg</t>
         </is>
       </c>
     </row>
@@ -3272,35 +3272,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_28.jpg</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_01.jpg</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_04.jpg</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_22.jpg</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="K33" t="n">
         <v>7</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_04.jpg</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>3</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_12.jpg</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>8</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_28.jpg</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>5</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -3360,44 +3360,44 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_29.jpg</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>3</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_21.jpg</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_08.jpg</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_16.jpg</t>
         </is>
       </c>
-      <c r="G34" t="n">
+      <c r="M34" t="n">
         <v>8</v>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>7</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>10</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_14.jpg</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
-        <v>6</v>
-      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_00.png</t>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_14.jpg</t>
+          <t>stimuli/hand/hand_16.jpg</t>
         </is>
       </c>
     </row>
@@ -3448,27 +3448,27 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_11.jpg</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_14.jpg</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>stimuli/house/house_31.jpg</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="I35" t="n">
         <v>9</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>10</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_14.jpg</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>4</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -3480,11 +3480,11 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_01.jpg</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_01.jpg</t>
         </is>
       </c>
     </row>
@@ -3536,11 +3536,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3552,61 +3552,61 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_01.jpg</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>10</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_14.jpg</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>6</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
-      <c r="I36" t="n">
+      <c r="M36" t="n">
         <v>9</v>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
         <is>
           <t>stimuli/bicycle/bicycle_29.jpg</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>2</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_08.jpg</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
-        <v>4</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_29.jpg</t>
         </is>
       </c>
     </row>
@@ -3624,44 +3624,44 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>stimuli/house/house_31.jpg</t>
+          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_12.jpg</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>8</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_04.jpg</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_22.jpg</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>7</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_10.jpg</t>
         </is>
       </c>
-      <c r="G37" t="n">
+      <c r="M37" t="n">
         <v>6</v>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_12.jpg</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>8</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_28.jpg</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>5</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_01.jpg</t>
-        </is>
-      </c>
-      <c r="M37" t="n">
-        <v>2</v>
-      </c>
       <c r="N37" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_03.png</t>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_01.jpg</t>
+          <t>stimuli/flower/flower_10.jpg</t>
         </is>
       </c>
     </row>
@@ -3712,11 +3712,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3728,27 +3728,27 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_29.jpg</t>
         </is>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>3</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_16.jpg</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
-        <v>8</v>
-      </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/dog/dog_21.jpg</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/dog/dog_21.jpg</t>
         </is>
       </c>
     </row>
@@ -3800,35 +3800,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_10.jpg</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_31.jpg</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>9</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_01.jpg</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="I39" t="n">
         <v>2</v>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_14.jpg</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>4</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_04.jpg</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>3</v>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_28.jpg</t>
+          <t>stimuli/hammer/hammer_22.jpg</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_01.jpg</t>
+          <t>stimuli/flower/flower_10.jpg</t>
         </is>
       </c>
     </row>
@@ -3888,11 +3888,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3904,28 +3904,28 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_01.jpg</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>10</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>9</v>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_08.jpg</t>
-        </is>
-      </c>
-      <c r="M40" t="n">
-        <v>4</v>
-      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_04.png</t>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/jacket/jacket_01.jpg</t>
         </is>
       </c>
     </row>
@@ -3976,35 +3976,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_04.jpg</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_12.jpg</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="G41" t="n">
         <v>8</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>stimuli/flower/flower_10.jpg</t>
         </is>
       </c>
-      <c r="G41" t="n">
+      <c r="I41" t="n">
         <v>6</v>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_01.jpg</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>2</v>
-      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_28.jpg</t>
+          <t>stimuli/hammer/hammer_22.jpg</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_12.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
     </row>
@@ -4064,44 +4064,44 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_35.jpg</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_10.jpg</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>9</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_01.jpg</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>10</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_21.jpg</t>
         </is>
       </c>
-      <c r="E42" t="n">
+      <c r="M42" t="n">
         <v>5</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_08.jpg</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>4</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_29.jpg</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>3</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_10.jpg</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>9</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
-        </is>
-      </c>
-      <c r="M42" t="n">
-        <v>7</v>
-      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_04.png</t>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/dog/dog_21.jpg</t>
         </is>
       </c>
     </row>
@@ -4152,35 +4152,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_01.jpg</t>
+          <t>stimuli/flower/flower_10.jpg</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_10.jpg</t>
+          <t>stimuli/hand/hand_12.jpg</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_28.jpg</t>
+          <t>stimuli/hammer/hammer_22.jpg</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -4240,11 +4240,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4256,27 +4256,27 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_29.jpg</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_16.jpg</t>
         </is>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>8</v>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_14.jpg</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
-        <v>6</v>
-      </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -4328,35 +4328,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_11.jpg</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>10</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_01.jpg</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_04.jpg</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
           <t>stimuli/house/house_31.jpg</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="K45" t="n">
         <v>9</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_04.jpg</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>3</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_12.jpg</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>8</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_14.jpg</t>
-        </is>
-      </c>
-      <c r="K45" t="n">
-        <v>4</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>stimuli/house/house_31.jpg</t>
+          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
     </row>
@@ -4416,77 +4416,77 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_14.jpg</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>6</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_21.jpg</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>5</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_08.jpg</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>4</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_16.jpg</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>8</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_29.jpg</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>7</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
-        </is>
-      </c>
-      <c r="K46" t="n">
-        <v>10</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_14.jpg</t>
-        </is>
-      </c>
-      <c r="M46" t="n">
-        <v>6</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_29.jpg</t>
         </is>
       </c>
     </row>
@@ -4504,43 +4504,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_11.jpg</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>10</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_14.jpg</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>4</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_12.jpg</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>8</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
           <t>stimuli/house/house_31.jpg</t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="K47" t="n">
         <v>9</v>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>10</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_10.jpg</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>6</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_14.jpg</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
-        <v>4</v>
-      </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_01.jpg</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/house/house_31.jpg</t>
         </is>
       </c>
     </row>
@@ -4592,11 +4592,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4608,61 +4608,61 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
+          <t>stimuli/house/house_10.jpg</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>9</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
-      <c r="I48" t="n">
+      <c r="K48" t="n">
         <v>4</v>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>stimuli/jacket/jacket_01.jpg</t>
         </is>
       </c>
-      <c r="K48" t="n">
+      <c r="M48" t="n">
         <v>10</v>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
         <is>
           <t>stimuli/house/house_10.jpg</t>
-        </is>
-      </c>
-      <c r="M48" t="n">
-        <v>9</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
     </row>
@@ -4680,27 +4680,27 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/dog/dog_28.jpg</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_10.jpg</t>
+          <t>stimuli/hand/hand_12.jpg</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_12.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -4712,11 +4712,11 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_01.jpg</t>
+          <t>stimuli/flower/flower_10.jpg</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_10.jpg</t>
+          <t>stimuli/hand/hand_12.jpg</t>
         </is>
       </c>
     </row>
@@ -4768,11 +4768,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4784,27 +4784,27 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
+          <t>stimuli/house/house_10.jpg</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>9</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
-      <c r="I50" t="n">
+      <c r="K50" t="n">
         <v>4</v>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>10</v>
-      </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_29.jpg</t>
+          <t>stimuli/flower/flower_14.jpg</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
     </row>
@@ -4856,44 +4856,44 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/dog/dog_28.jpg</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_12.jpg</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>8</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_04.jpg</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_31.jpg</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>9</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_10.jpg</t>
         </is>
       </c>
-      <c r="G51" t="n">
+      <c r="M51" t="n">
         <v>6</v>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_12.jpg</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>8</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_14.jpg</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>4</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_01.jpg</t>
-        </is>
-      </c>
-      <c r="M51" t="n">
-        <v>2</v>
-      </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_04.png</t>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/dog/dog_28.jpg</t>
         </is>
       </c>
     </row>
@@ -4944,11 +4944,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4960,27 +4960,27 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_16.jpg</t>
+          <t>stimuli/bread/bread_29.jpg</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/jacket/jacket_01.jpg</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_29.jpg</t>
+          <t>stimuli/flower/flower_14.jpg</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/jacket/jacket_01.jpg</t>
         </is>
       </c>
     </row>
@@ -5032,77 +5032,77 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>stimuli/house/house_31.jpg</t>
+          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_10.jpg</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>6</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_04.jpg</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>3</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_22.jpg</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>7</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_01.jpg</t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="M53" t="n">
         <v>2</v>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_12.jpg</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>8</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_28.jpg</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>5</v>
-      </c>
-      <c r="L53" t="inlineStr">
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
         <is>
           <t>stimuli/bread/bread_04.jpg</t>
-        </is>
-      </c>
-      <c r="M53" t="n">
-        <v>3</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_12.jpg</t>
         </is>
       </c>
     </row>
@@ -5120,44 +5120,44 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/dog/dog_21.jpg</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_29.jpg</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>3</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_16.jpg</t>
         </is>
       </c>
-      <c r="G54" t="n">
+      <c r="I54" t="n">
         <v>8</v>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_14.jpg</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>6</v>
-      </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_08.jpg</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>4</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_01.jpg</t>
         </is>
       </c>
-      <c r="K54" t="n">
+      <c r="M54" t="n">
         <v>10</v>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_10.jpg</t>
-        </is>
-      </c>
-      <c r="M54" t="n">
-        <v>9</v>
-      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_03.png</t>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_16.jpg</t>
+          <t>stimuli/bread/bread_29.jpg</t>
         </is>
       </c>
     </row>
@@ -5208,27 +5208,27 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>stimuli/house/house_31.jpg</t>
+          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/dog/dog_28.jpg</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -5240,11 +5240,11 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_01.jpg</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -5296,77 +5296,77 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_14.jpg</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>6</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_21.jpg</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>5</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_08.jpg</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>4</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_01.jpg</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>10</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_29.jpg</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>2</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>7</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
-        </is>
-      </c>
-      <c r="K56" t="n">
-        <v>10</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_10.jpg</t>
-        </is>
-      </c>
-      <c r="M56" t="n">
-        <v>9</v>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_29.jpg</t>
         </is>
       </c>
     </row>
@@ -5384,44 +5384,44 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>stimuli/house/house_31.jpg</t>
+          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_12.jpg</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>8</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_01.jpg</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>2</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_10.jpg</t>
         </is>
       </c>
-      <c r="I57" t="n">
+      <c r="M57" t="n">
         <v>6</v>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_04.jpg</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>3</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_01.jpg</t>
-        </is>
-      </c>
-      <c r="M57" t="n">
-        <v>2</v>
-      </c>
       <c r="N57" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_03.png</t>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_10.jpg</t>
+          <t>stimuli/hand/hand_12.jpg</t>
         </is>
       </c>
     </row>
@@ -5472,11 +5472,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5488,27 +5488,27 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_16.jpg</t>
+          <t>stimuli/bread/bread_29.jpg</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/jacket/jacket_01.jpg</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_29.jpg</t>
+          <t>stimuli/flower/flower_14.jpg</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5560,44 +5560,44 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>stimuli/house/house_31.jpg</t>
+          <t>stimuli/jacket/jacket_11.jpg</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_10.jpg</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>6</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_04.jpg</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>3</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_22.jpg</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>7</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_01.jpg</t>
         </is>
       </c>
-      <c r="G59" t="n">
+      <c r="M59" t="n">
         <v>2</v>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_12.jpg</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>8</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_28.jpg</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
-        <v>5</v>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_04.jpg</t>
-        </is>
-      </c>
-      <c r="M59" t="n">
-        <v>3</v>
-      </c>
       <c r="N59" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_05.png</t>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_01.jpg</t>
+          <t>stimuli/flower/flower_10.jpg</t>
         </is>
       </c>
     </row>
@@ -5648,77 +5648,77 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_35.jpg</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>7</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_16.jpg</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>8</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_29.jpg</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>2</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_14.jpg</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>6</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_21.jpg</t>
         </is>
       </c>
-      <c r="E60" t="n">
+      <c r="M60" t="n">
         <v>5</v>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
         <is>
           <t>stimuli/flower/flower_14.jpg</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>6</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_29.jpg</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>3</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_29.jpg</t>
-        </is>
-      </c>
-      <c r="K60" t="n">
-        <v>2</v>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
-        </is>
-      </c>
-      <c r="M60" t="n">
-        <v>7</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_29.jpg</t>
         </is>
       </c>
     </row>
@@ -5736,43 +5736,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_01.jpg</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_11.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_10.jpg</t>
+          <t>stimuli/hand/hand_12.jpg</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_28.jpg</t>
+          <t>stimuli/hammer/hammer_22.jpg</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/house/house_31.jpg</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_10.jpg</t>
+          <t>stimuli/hand/hand_12.jpg</t>
         </is>
       </c>
     </row>
